--- a/5_Isolates/Isolates_summary.xlsx
+++ b/5_Isolates/Isolates_summary.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jy/Desktop/Nanopore-Adaptive-Sequencing/5_Isolates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB631A7-3FCF-0E49-9C8B-23103596132E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7677E9F-954A-024B-93ED-A307A1A434AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{83819237-C7AC-FD40-9E91-27D3D43085C6}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="1" activeTab="1" xr2:uid="{83819237-C7AC-FD40-9E91-27D3D43085C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S4 Isolates Abundance" sheetId="5" r:id="rId1"/>
-    <sheet name="gtdbtk_Isolates_annotation" sheetId="6" r:id="rId2"/>
-    <sheet name="hatch2026" sheetId="7" r:id="rId3"/>
+    <sheet name="colony culture" sheetId="9" r:id="rId2"/>
+    <sheet name="gtdbtk_Isolates_annotation" sheetId="6" r:id="rId3"/>
+    <sheet name="hatch2026" sheetId="7" r:id="rId4"/>
+    <sheet name="L4 CFU per ml" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="426">
   <si>
     <t>Isolate Genomes Abundance (% of reads mapped)</t>
   </si>
@@ -1145,13 +1147,184 @@
   </si>
   <si>
     <t>submission1_id2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolate </t>
+  </si>
+  <si>
+    <t>Rep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dilution </t>
+  </si>
+  <si>
+    <t>Colony</t>
+  </si>
+  <si>
+    <t>dead</t>
+  </si>
+  <si>
+    <t>Conv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFUper_ml </t>
+  </si>
+  <si>
+    <t>CFUper_larvae</t>
+  </si>
+  <si>
+    <t>Counts</t>
+  </si>
+  <si>
+    <t>dilution</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>CFU/mL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024 HGT Larval Homogenate Plate Counts on LB and Chromo Agar </t>
+  </si>
+  <si>
+    <t>10 ul of 100 ul homogenate into 90 ul NaCl, 10 ul dilution plated</t>
+  </si>
+  <si>
+    <t>Log10(LB)</t>
+  </si>
+  <si>
+    <t>Log10(Chr)</t>
+  </si>
+  <si>
+    <t>Water Source</t>
+  </si>
+  <si>
+    <t>Larvae</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>Chromo</t>
+  </si>
+  <si>
+    <t>LB (CFU/ml)</t>
+  </si>
+  <si>
+    <t>Chromo (CFU/ml)</t>
+  </si>
+  <si>
+    <t>LB (CFU/Larvae)</t>
+  </si>
+  <si>
+    <t>Chromo (CFU/Larvae)</t>
+  </si>
+  <si>
+    <t>Chr</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>lsd</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>TL5</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>TL6</t>
+  </si>
+  <si>
+    <t>HL5</t>
+  </si>
+  <si>
+    <t>HL6</t>
+  </si>
+  <si>
+    <t>GL1</t>
+  </si>
+  <si>
+    <t>GL3</t>
+  </si>
+  <si>
+    <t>GL5</t>
+  </si>
+  <si>
+    <t>GL6</t>
+  </si>
+  <si>
+    <t>18*10E7</t>
+  </si>
+  <si>
+    <t>8*10E87</t>
+  </si>
+  <si>
+    <t>0.6*10E7</t>
+  </si>
+  <si>
+    <t>live</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>chi-square test</t>
+  </si>
+  <si>
+    <t>Fisher's exact test</t>
+  </si>
+  <si>
+    <t>X-squared = 23.476, df = 6, p-value = 0.0006517</t>
+  </si>
+  <si>
+    <t>X-squared = 50.346, df = 8, p-value = 3.506e-08</t>
+  </si>
+  <si>
+    <t>group1</t>
+  </si>
+  <si>
+    <t>group2</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>p_adjusted</t>
+  </si>
+  <si>
+    <t>Revision3: check the sig for LB+Chromo</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Plates</t>
+  </si>
+  <si>
+    <t>CFU_Larvae</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1210,8 +1383,41 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Monaco"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Sans"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1241,8 +1447,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1394,12 +1606,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1443,10 +1690,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1791,23 +2074,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8602EA5-1E8C-EE4B-9E08-F3E5445F5F61}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="21.1640625" customWidth="1"/>
     <col min="4" max="4" width="22.33203125" customWidth="1"/>
     <col min="5" max="5" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
@@ -1823,7 +2106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
@@ -1836,7 +2119,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1853,8 +2136,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="37" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="64" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1870,8 +2153,8 @@
         <v>4.0423999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="37"/>
+    <row r="6" spans="1:6">
+      <c r="A6" s="64"/>
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1885,8 +2168,8 @@
         <v>3.2513999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="37"/>
+    <row r="7" spans="1:6">
+      <c r="A7" s="64"/>
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1900,8 +2183,8 @@
         <v>0.84970000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="37" t="s">
+    <row r="8" spans="1:6">
+      <c r="A8" s="64" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1917,8 +2200,8 @@
         <v>2.4424999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
+    <row r="9" spans="1:6">
+      <c r="A9" s="64"/>
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
@@ -1932,8 +2215,8 @@
         <v>1.9065000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="37"/>
+    <row r="10" spans="1:6">
+      <c r="A10" s="64"/>
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1947,8 +2230,8 @@
         <v>0.52939999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="37" t="s">
+    <row r="11" spans="1:6">
+      <c r="A11" s="64" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1964,8 +2247,8 @@
         <v>19.217500000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="37"/>
+    <row r="12" spans="1:6">
+      <c r="A12" s="64"/>
       <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
@@ -1979,8 +2262,8 @@
         <v>17.668800000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="37"/>
+    <row r="13" spans="1:6">
+      <c r="A13" s="64"/>
       <c r="B13" s="1" t="s">
         <v>24</v>
       </c>
@@ -2006,11 +2289,2071 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD257ABE-7CB1-6447-A330-B367B5545E5D}">
+  <dimension ref="A1:W65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="I1" s="66" t="s">
+        <v>381</v>
+      </c>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="68"/>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="12">
+        <v>11.672097857935718</v>
+      </c>
+      <c r="C2" s="12">
+        <v>6</v>
+      </c>
+      <c r="D2" s="12">
+        <v>47</v>
+      </c>
+      <c r="E2" s="40">
+        <v>10000000000</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F25" si="0">LOG(D2*E2)</f>
+        <v>11.672097857935718</v>
+      </c>
+      <c r="G2" s="38">
+        <f t="shared" ref="G2:G25" si="1">D2*E2</f>
+        <v>470000000000</v>
+      </c>
+      <c r="I2" s="66" t="s">
+        <v>382</v>
+      </c>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="68"/>
+      <c r="R2" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="S2" s="42" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="12">
+        <v>11.414973347970818</v>
+      </c>
+      <c r="C3" s="12">
+        <v>6</v>
+      </c>
+      <c r="D3" s="12">
+        <v>26</v>
+      </c>
+      <c r="E3" s="40">
+        <v>10000000000</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>11.414973347970818</v>
+      </c>
+      <c r="G3" s="38">
+        <f t="shared" si="1"/>
+        <v>260000000000</v>
+      </c>
+      <c r="I3" s="43" t="s">
+        <v>385</v>
+      </c>
+      <c r="J3" s="43" t="s">
+        <v>386</v>
+      </c>
+      <c r="K3" s="43" t="s">
+        <v>378</v>
+      </c>
+      <c r="L3" s="43" t="s">
+        <v>387</v>
+      </c>
+      <c r="M3" s="43" t="s">
+        <v>388</v>
+      </c>
+      <c r="N3" s="43" t="s">
+        <v>389</v>
+      </c>
+      <c r="O3" s="43" t="s">
+        <v>390</v>
+      </c>
+      <c r="P3" s="43" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q3" s="43" t="s">
+        <v>392</v>
+      </c>
+      <c r="R3" s="42" t="s">
+        <v>387</v>
+      </c>
+      <c r="S3" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="T3" s="42" t="s">
+        <v>394</v>
+      </c>
+      <c r="U3" s="42" t="s">
+        <v>395</v>
+      </c>
+      <c r="V3" s="42" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="12">
+        <v>11.361727836017593</v>
+      </c>
+      <c r="C4" s="12">
+        <v>6</v>
+      </c>
+      <c r="D4" s="12">
+        <v>23</v>
+      </c>
+      <c r="E4" s="40">
+        <v>10000000000</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>11.361727836017593</v>
+      </c>
+      <c r="G4" s="38">
+        <f t="shared" si="1"/>
+        <v>230000000000</v>
+      </c>
+      <c r="I4" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="K4" s="43">
+        <v>4</v>
+      </c>
+      <c r="L4" s="43">
+        <v>18</v>
+      </c>
+      <c r="M4" s="43">
+        <v>25</v>
+      </c>
+      <c r="N4" s="43">
+        <f>L4 * 10^(K4 + 2)</f>
+        <v>18000000</v>
+      </c>
+      <c r="O4" s="43">
+        <f>M4 * 10^(K4 + 2)</f>
+        <v>25000000</v>
+      </c>
+      <c r="P4" s="37">
+        <f>N4/10</f>
+        <v>1800000</v>
+      </c>
+      <c r="Q4" s="37">
+        <f>O4/10</f>
+        <v>2500000</v>
+      </c>
+      <c r="R4">
+        <f>LOG10(P4)</f>
+        <v>6.2552725051033065</v>
+      </c>
+      <c r="S4">
+        <f>LOG10(Q4)</f>
+        <v>6.3979400086720375</v>
+      </c>
+      <c r="T4" t="s">
+        <v>256</v>
+      </c>
+      <c r="U4" t="s">
+        <v>397</v>
+      </c>
+      <c r="V4" s="38">
+        <f>AVERAGE(P4:Q9)</f>
+        <v>6481818.1818181816</v>
+      </c>
+      <c r="W4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="12">
+        <v>8.9542425094393252</v>
+      </c>
+      <c r="C5" s="12">
+        <v>4</v>
+      </c>
+      <c r="D5" s="12">
+        <v>9</v>
+      </c>
+      <c r="E5" s="40">
+        <v>100000000</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>8.9542425094393252</v>
+      </c>
+      <c r="G5" s="38">
+        <f t="shared" si="1"/>
+        <v>900000000</v>
+      </c>
+      <c r="I5" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="K5" s="43">
+        <v>4</v>
+      </c>
+      <c r="L5" s="43">
+        <v>8</v>
+      </c>
+      <c r="M5" s="43">
+        <v>9</v>
+      </c>
+      <c r="N5" s="43">
+        <f t="shared" ref="N5:N21" si="2">L5 * 10^(K5 + 2)</f>
+        <v>8000000</v>
+      </c>
+      <c r="O5" s="43">
+        <f t="shared" ref="O5:O21" si="3">M5 * 10^(K5 + 2)</f>
+        <v>9000000</v>
+      </c>
+      <c r="P5" s="37">
+        <f t="shared" ref="P5:Q21" si="4">N5/10</f>
+        <v>800000</v>
+      </c>
+      <c r="Q5" s="37">
+        <f t="shared" si="4"/>
+        <v>900000</v>
+      </c>
+      <c r="R5">
+        <f>LOG10(P5)</f>
+        <v>5.9030899869919438</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S21" si="5">LOG10(Q5)</f>
+        <v>5.9542425094393252</v>
+      </c>
+      <c r="T5" t="s">
+        <v>256</v>
+      </c>
+      <c r="U5" t="s">
+        <v>397</v>
+      </c>
+      <c r="V5" s="38">
+        <f>STDEV(P4:Q9)/SQRT(11)</f>
+        <v>2645195.2387753292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="12">
+        <v>10.146128035678238</v>
+      </c>
+      <c r="C6" s="12">
+        <v>5</v>
+      </c>
+      <c r="D6" s="12">
+        <v>14</v>
+      </c>
+      <c r="E6" s="40">
+        <v>1000000000</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>10.146128035678238</v>
+      </c>
+      <c r="G6" s="38">
+        <f t="shared" si="1"/>
+        <v>14000000000</v>
+      </c>
+      <c r="I6" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="K6" s="43">
+        <v>5</v>
+      </c>
+      <c r="L6" s="43">
+        <v>23</v>
+      </c>
+      <c r="M6" s="43">
+        <v>24</v>
+      </c>
+      <c r="N6" s="43">
+        <f t="shared" si="2"/>
+        <v>230000000</v>
+      </c>
+      <c r="O6" s="43">
+        <f t="shared" si="3"/>
+        <v>240000000</v>
+      </c>
+      <c r="P6" s="37">
+        <f t="shared" si="4"/>
+        <v>23000000</v>
+      </c>
+      <c r="Q6" s="37">
+        <f t="shared" si="4"/>
+        <v>24000000</v>
+      </c>
+      <c r="R6">
+        <f>LOG10(P6)</f>
+        <v>7.3617278360175931</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="5"/>
+        <v>7.3802112417116064</v>
+      </c>
+      <c r="T6" t="s">
+        <v>256</v>
+      </c>
+      <c r="U6" t="s">
+        <v>397</v>
+      </c>
+      <c r="V6" s="38"/>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="12">
+        <v>11.857332496431269</v>
+      </c>
+      <c r="C7" s="12">
+        <v>6</v>
+      </c>
+      <c r="D7" s="12">
+        <v>72</v>
+      </c>
+      <c r="E7" s="40">
+        <v>10000000000</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>11.857332496431269</v>
+      </c>
+      <c r="G7" s="38">
+        <f t="shared" si="1"/>
+        <v>720000000000</v>
+      </c>
+      <c r="I7" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="K7" s="43">
+        <v>4</v>
+      </c>
+      <c r="L7" s="43">
+        <v>5</v>
+      </c>
+      <c r="M7" s="43">
+        <v>8</v>
+      </c>
+      <c r="N7" s="43">
+        <f t="shared" si="2"/>
+        <v>5000000</v>
+      </c>
+      <c r="O7" s="43">
+        <f t="shared" si="3"/>
+        <v>8000000</v>
+      </c>
+      <c r="P7" s="37">
+        <f t="shared" si="4"/>
+        <v>500000</v>
+      </c>
+      <c r="Q7" s="37">
+        <f t="shared" si="4"/>
+        <v>800000</v>
+      </c>
+      <c r="R7">
+        <f>LOG10(P7)</f>
+        <v>5.6989700043360187</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="5"/>
+        <v>5.9030899869919438</v>
+      </c>
+      <c r="T7" t="s">
+        <v>256</v>
+      </c>
+      <c r="U7" t="s">
+        <v>397</v>
+      </c>
+      <c r="V7" s="38"/>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="12">
+        <v>10.568201724066995</v>
+      </c>
+      <c r="C8" s="12">
+        <v>5</v>
+      </c>
+      <c r="D8" s="12">
+        <v>37</v>
+      </c>
+      <c r="E8" s="40">
+        <v>1000000000</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>10.568201724066995</v>
+      </c>
+      <c r="G8" s="38">
+        <f t="shared" si="1"/>
+        <v>37000000000</v>
+      </c>
+      <c r="I8" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="43" t="s">
+        <v>398</v>
+      </c>
+      <c r="K8" s="43">
+        <v>5</v>
+      </c>
+      <c r="L8" s="43" t="s">
+        <v>399</v>
+      </c>
+      <c r="M8" s="43">
+        <v>9</v>
+      </c>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43">
+        <f t="shared" si="3"/>
+        <v>90000000</v>
+      </c>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37">
+        <f t="shared" si="4"/>
+        <v>9000000</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="5"/>
+        <v>6.9542425094393252</v>
+      </c>
+      <c r="T8" t="s">
+        <v>256</v>
+      </c>
+      <c r="U8" t="s">
+        <v>397</v>
+      </c>
+      <c r="V8" s="38"/>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="12">
+        <v>10.380211241711606</v>
+      </c>
+      <c r="C9" s="12">
+        <v>5</v>
+      </c>
+      <c r="D9" s="12">
+        <v>24</v>
+      </c>
+      <c r="E9" s="40">
+        <v>1000000000</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>10.380211241711606</v>
+      </c>
+      <c r="G9" s="38">
+        <f t="shared" si="1"/>
+        <v>24000000000</v>
+      </c>
+      <c r="I9" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="K9" s="43">
+        <v>5</v>
+      </c>
+      <c r="L9" s="43">
+        <v>3</v>
+      </c>
+      <c r="M9" s="43">
+        <v>5</v>
+      </c>
+      <c r="N9" s="43">
+        <f t="shared" si="2"/>
+        <v>30000000</v>
+      </c>
+      <c r="O9" s="43">
+        <f t="shared" si="3"/>
+        <v>50000000</v>
+      </c>
+      <c r="P9" s="37">
+        <f t="shared" si="4"/>
+        <v>3000000</v>
+      </c>
+      <c r="Q9" s="37">
+        <f t="shared" si="4"/>
+        <v>5000000</v>
+      </c>
+      <c r="R9">
+        <f>LOG10(P9)</f>
+        <v>6.4771212547196626</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="5"/>
+        <v>6.6989700043360187</v>
+      </c>
+      <c r="T9" t="s">
+        <v>256</v>
+      </c>
+      <c r="U9" t="s">
+        <v>397</v>
+      </c>
+      <c r="V9" s="38"/>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="12">
+        <v>9.9542425094393252</v>
+      </c>
+      <c r="C10" s="12">
+        <v>5</v>
+      </c>
+      <c r="D10" s="12">
+        <v>9</v>
+      </c>
+      <c r="E10" s="40">
+        <v>1000000000</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>9.9542425094393252</v>
+      </c>
+      <c r="G10" s="38">
+        <f t="shared" si="1"/>
+        <v>9000000000</v>
+      </c>
+      <c r="I10" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="K10" s="43">
+        <v>5</v>
+      </c>
+      <c r="L10" s="43">
+        <v>9</v>
+      </c>
+      <c r="M10" s="43">
+        <v>8</v>
+      </c>
+      <c r="N10" s="43">
+        <f t="shared" si="2"/>
+        <v>90000000</v>
+      </c>
+      <c r="O10" s="43">
+        <f t="shared" si="3"/>
+        <v>80000000</v>
+      </c>
+      <c r="P10" s="37">
+        <f t="shared" si="4"/>
+        <v>9000000</v>
+      </c>
+      <c r="Q10" s="37">
+        <f t="shared" si="4"/>
+        <v>8000000</v>
+      </c>
+      <c r="R10">
+        <f>LOG10(P10)</f>
+        <v>6.9542425094393252</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="5"/>
+        <v>6.9030899869919438</v>
+      </c>
+      <c r="T10" t="s">
+        <v>164</v>
+      </c>
+      <c r="U10" t="s">
+        <v>397</v>
+      </c>
+      <c r="V10" s="38">
+        <f>AVERAGE(P10:Q15)</f>
+        <v>84694792.624765784</v>
+      </c>
+      <c r="W10" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="12">
+        <v>11.361727836017593</v>
+      </c>
+      <c r="C11" s="12">
+        <v>6</v>
+      </c>
+      <c r="D11" s="12">
+        <v>23</v>
+      </c>
+      <c r="E11" s="40">
+        <v>10000000000</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>11.361727836017593</v>
+      </c>
+      <c r="G11" s="38">
+        <f t="shared" si="1"/>
+        <v>230000000000</v>
+      </c>
+      <c r="I11" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="K11" s="43">
+        <v>5</v>
+      </c>
+      <c r="L11" s="43" t="s">
+        <v>399</v>
+      </c>
+      <c r="M11" s="43">
+        <v>20</v>
+      </c>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43">
+        <f t="shared" si="3"/>
+        <v>200000000</v>
+      </c>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37">
+        <f t="shared" si="4"/>
+        <v>20000000</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="5"/>
+        <v>7.3010299956639813</v>
+      </c>
+      <c r="T11" t="s">
+        <v>164</v>
+      </c>
+      <c r="U11" t="s">
+        <v>397</v>
+      </c>
+      <c r="V11" s="38">
+        <f>STDEV(P10:Q15)/SQRT(11)</f>
+        <v>34291615.609852545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="12">
+        <v>9.4913616938342731</v>
+      </c>
+      <c r="C12" s="12">
+        <v>4</v>
+      </c>
+      <c r="D12" s="12">
+        <v>31</v>
+      </c>
+      <c r="E12" s="40">
+        <v>100000000</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>9.4913616938342731</v>
+      </c>
+      <c r="G12" s="38">
+        <f t="shared" si="1"/>
+        <v>3100000000</v>
+      </c>
+      <c r="I12" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="K12" s="43">
+        <v>4</v>
+      </c>
+      <c r="L12" s="43">
+        <v>11</v>
+      </c>
+      <c r="M12" s="43">
+        <v>31</v>
+      </c>
+      <c r="N12" s="43">
+        <f t="shared" si="2"/>
+        <v>11000000</v>
+      </c>
+      <c r="O12" s="43">
+        <f t="shared" si="3"/>
+        <v>31000000</v>
+      </c>
+      <c r="P12" s="37">
+        <f t="shared" si="4"/>
+        <v>1100000</v>
+      </c>
+      <c r="Q12" s="37">
+        <f t="shared" si="4"/>
+        <v>3100000</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ref="R12:R21" si="6">LOG10(P12)</f>
+        <v>6.0413926851582254</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="5"/>
+        <v>6.4913616938342731</v>
+      </c>
+      <c r="T12" t="s">
+        <v>164</v>
+      </c>
+      <c r="U12" t="s">
+        <v>397</v>
+      </c>
+      <c r="V12" s="38"/>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B13" s="12">
+        <v>9.0413926851582254</v>
+      </c>
+      <c r="C13" s="12">
+        <v>4</v>
+      </c>
+      <c r="D13" s="12">
+        <v>11</v>
+      </c>
+      <c r="E13" s="40">
+        <v>100000000</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>9.0413926851582254</v>
+      </c>
+      <c r="G13" s="38">
+        <f t="shared" si="1"/>
+        <v>1100000000</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="K13" s="43">
+        <v>3.5</v>
+      </c>
+      <c r="L13" s="43">
+        <v>5</v>
+      </c>
+      <c r="M13" s="43">
+        <v>9</v>
+      </c>
+      <c r="N13" s="43">
+        <f t="shared" si="2"/>
+        <v>1581138.8300841909</v>
+      </c>
+      <c r="O13" s="43">
+        <f t="shared" si="3"/>
+        <v>2846049.8941515437</v>
+      </c>
+      <c r="P13" s="37">
+        <f t="shared" si="4"/>
+        <v>158113.8830084191</v>
+      </c>
+      <c r="Q13" s="37">
+        <f t="shared" si="4"/>
+        <v>284604.98941515438</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="6"/>
+        <v>5.1989700043360187</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="5"/>
+        <v>5.4542425094393252</v>
+      </c>
+      <c r="T13" t="s">
+        <v>164</v>
+      </c>
+      <c r="U13" t="s">
+        <v>397</v>
+      </c>
+      <c r="V13" s="38"/>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B14" s="12">
+        <v>9.9030899869919438</v>
+      </c>
+      <c r="C14" s="12">
+        <v>5</v>
+      </c>
+      <c r="D14" s="12">
+        <v>8</v>
+      </c>
+      <c r="E14" s="40">
+        <v>1000000000</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>9.9030899869919438</v>
+      </c>
+      <c r="G14" s="38">
+        <f t="shared" si="1"/>
+        <v>8000000000</v>
+      </c>
+      <c r="I14" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="K14" s="43">
+        <v>6</v>
+      </c>
+      <c r="L14" s="43">
+        <v>14</v>
+      </c>
+      <c r="M14" s="43">
+        <v>23</v>
+      </c>
+      <c r="N14" s="43">
+        <f t="shared" si="2"/>
+        <v>1400000000</v>
+      </c>
+      <c r="O14" s="43">
+        <f t="shared" si="3"/>
+        <v>2300000000</v>
+      </c>
+      <c r="P14" s="37">
+        <f t="shared" si="4"/>
+        <v>140000000</v>
+      </c>
+      <c r="Q14" s="37">
+        <f t="shared" si="4"/>
+        <v>230000000</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="6"/>
+        <v>8.1461280356782382</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="5"/>
+        <v>8.3617278360175931</v>
+      </c>
+      <c r="T14" t="s">
+        <v>164</v>
+      </c>
+      <c r="U14" t="s">
+        <v>397</v>
+      </c>
+      <c r="V14" s="38"/>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="12">
+        <v>8.6989700043360187</v>
+      </c>
+      <c r="C15" s="41">
+        <v>4</v>
+      </c>
+      <c r="D15" s="12">
+        <v>5</v>
+      </c>
+      <c r="E15" s="40">
+        <v>100000000</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>8.6989700043360187</v>
+      </c>
+      <c r="G15" s="38">
+        <f t="shared" si="1"/>
+        <v>500000000</v>
+      </c>
+      <c r="I15" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="K15" s="43">
+        <v>6</v>
+      </c>
+      <c r="L15" s="43">
+        <v>26</v>
+      </c>
+      <c r="M15" s="43">
+        <v>26</v>
+      </c>
+      <c r="N15" s="43">
+        <f t="shared" si="2"/>
+        <v>2600000000</v>
+      </c>
+      <c r="O15" s="43">
+        <f t="shared" si="3"/>
+        <v>2600000000</v>
+      </c>
+      <c r="P15" s="37">
+        <f t="shared" si="4"/>
+        <v>260000000</v>
+      </c>
+      <c r="Q15" s="37">
+        <f t="shared" si="4"/>
+        <v>260000000</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="6"/>
+        <v>8.4149733479708182</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="5"/>
+        <v>8.4149733479708182</v>
+      </c>
+      <c r="T15" t="s">
+        <v>164</v>
+      </c>
+      <c r="U15" t="s">
+        <v>397</v>
+      </c>
+      <c r="V15" s="38"/>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="12">
+        <v>10.301029995663981</v>
+      </c>
+      <c r="C16" s="12">
+        <v>5</v>
+      </c>
+      <c r="D16" s="12">
+        <v>20</v>
+      </c>
+      <c r="E16" s="40">
+        <v>1000000000</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>10.301029995663981</v>
+      </c>
+      <c r="G16" s="38">
+        <f t="shared" si="1"/>
+        <v>20000000000</v>
+      </c>
+      <c r="I16" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>403</v>
+      </c>
+      <c r="K16" s="43">
+        <v>6</v>
+      </c>
+      <c r="L16" s="43">
+        <v>32</v>
+      </c>
+      <c r="M16" s="43">
+        <v>47</v>
+      </c>
+      <c r="N16" s="43">
+        <f t="shared" si="2"/>
+        <v>3200000000</v>
+      </c>
+      <c r="O16" s="43">
+        <f t="shared" si="3"/>
+        <v>4700000000</v>
+      </c>
+      <c r="P16" s="37">
+        <f t="shared" si="4"/>
+        <v>320000000</v>
+      </c>
+      <c r="Q16" s="37">
+        <f t="shared" si="4"/>
+        <v>470000000</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="6"/>
+        <v>8.5051499783199063</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="5"/>
+        <v>8.672097857935718</v>
+      </c>
+      <c r="T16" t="s">
+        <v>61</v>
+      </c>
+      <c r="U16" t="s">
+        <v>397</v>
+      </c>
+      <c r="V16" s="38">
+        <f>AVERAGE(P16:Q21)</f>
+        <v>176400000</v>
+      </c>
+      <c r="W16" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
+      <c r="A17" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17">
+        <v>9.9030899869919438</v>
+      </c>
+      <c r="C17" s="12">
+        <v>5</v>
+      </c>
+      <c r="D17" s="12">
+        <v>8</v>
+      </c>
+      <c r="E17" s="38">
+        <v>1000000000</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>9.9030899869919438</v>
+      </c>
+      <c r="G17" s="38">
+        <f t="shared" si="1"/>
+        <v>8000000000</v>
+      </c>
+      <c r="I17" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="K17" s="43">
+        <v>5</v>
+      </c>
+      <c r="L17" s="43">
+        <v>14</v>
+      </c>
+      <c r="M17" s="43">
+        <v>24</v>
+      </c>
+      <c r="N17" s="43">
+        <f t="shared" si="2"/>
+        <v>140000000</v>
+      </c>
+      <c r="O17" s="43">
+        <f t="shared" si="3"/>
+        <v>240000000</v>
+      </c>
+      <c r="P17" s="37">
+        <f t="shared" si="4"/>
+        <v>14000000</v>
+      </c>
+      <c r="Q17" s="37">
+        <f t="shared" si="4"/>
+        <v>24000000</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="6"/>
+        <v>7.1461280356782382</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="5"/>
+        <v>7.3802112417116064</v>
+      </c>
+      <c r="T17" t="s">
+        <v>61</v>
+      </c>
+      <c r="U17" t="s">
+        <v>397</v>
+      </c>
+      <c r="V17" s="38">
+        <f>STDEV(P16:Q21)/SQRT(12)</f>
+        <v>71515049.274451837</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
+      <c r="A18" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" s="12">
+        <v>9.3979400086720375</v>
+      </c>
+      <c r="C18" s="12">
+        <v>4</v>
+      </c>
+      <c r="D18" s="12">
+        <v>25</v>
+      </c>
+      <c r="E18" s="40">
+        <v>100000000</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>9.3979400086720375</v>
+      </c>
+      <c r="G18" s="38">
+        <f t="shared" si="1"/>
+        <v>2500000000</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="43" t="s">
+        <v>404</v>
+      </c>
+      <c r="K18" s="43">
+        <v>6</v>
+      </c>
+      <c r="L18" s="43">
+        <v>45</v>
+      </c>
+      <c r="M18" s="43">
+        <v>72</v>
+      </c>
+      <c r="N18" s="43">
+        <f t="shared" si="2"/>
+        <v>4500000000</v>
+      </c>
+      <c r="O18" s="43">
+        <f t="shared" si="3"/>
+        <v>7200000000</v>
+      </c>
+      <c r="P18" s="37">
+        <f t="shared" si="4"/>
+        <v>450000000</v>
+      </c>
+      <c r="Q18" s="37">
+        <f t="shared" si="4"/>
+        <v>720000000</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="6"/>
+        <v>8.653212513775344</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="5"/>
+        <v>8.857332496431269</v>
+      </c>
+      <c r="T18" t="s">
+        <v>61</v>
+      </c>
+      <c r="U18" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
+      <c r="A19" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" s="12">
+        <v>10.361727836017593</v>
+      </c>
+      <c r="C19" s="12">
+        <v>5</v>
+      </c>
+      <c r="D19" s="12">
+        <v>23</v>
+      </c>
+      <c r="E19" s="40">
+        <v>1000000000</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>10.361727836017593</v>
+      </c>
+      <c r="G19" s="38">
+        <f t="shared" si="1"/>
+        <v>23000000000</v>
+      </c>
+      <c r="I19" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="K19" s="43">
+        <v>5</v>
+      </c>
+      <c r="L19" s="43">
+        <v>31</v>
+      </c>
+      <c r="M19" s="43">
+        <v>37</v>
+      </c>
+      <c r="N19" s="43">
+        <f t="shared" si="2"/>
+        <v>310000000</v>
+      </c>
+      <c r="O19" s="43">
+        <f t="shared" si="3"/>
+        <v>370000000</v>
+      </c>
+      <c r="P19" s="37">
+        <f t="shared" si="4"/>
+        <v>31000000</v>
+      </c>
+      <c r="Q19" s="37">
+        <f t="shared" si="4"/>
+        <v>37000000</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="6"/>
+        <v>7.4913616938342731</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="5"/>
+        <v>7.568201724066995</v>
+      </c>
+      <c r="T19" t="s">
+        <v>61</v>
+      </c>
+      <c r="U19" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
+      <c r="A20" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B20" s="12">
+        <v>8.6989700043360187</v>
+      </c>
+      <c r="C20" s="12">
+        <v>4</v>
+      </c>
+      <c r="D20" s="12">
+        <v>5</v>
+      </c>
+      <c r="E20" s="40">
+        <v>100000000</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>8.6989700043360187</v>
+      </c>
+      <c r="G20" s="38">
+        <f t="shared" si="1"/>
+        <v>500000000</v>
+      </c>
+      <c r="I20" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="43" t="s">
+        <v>405</v>
+      </c>
+      <c r="K20" s="43">
+        <v>4</v>
+      </c>
+      <c r="L20" s="43">
+        <v>9</v>
+      </c>
+      <c r="M20" s="43">
+        <v>9</v>
+      </c>
+      <c r="N20" s="43">
+        <f t="shared" si="2"/>
+        <v>9000000</v>
+      </c>
+      <c r="O20" s="43">
+        <f t="shared" si="3"/>
+        <v>9000000</v>
+      </c>
+      <c r="P20" s="37">
+        <f t="shared" si="4"/>
+        <v>900000</v>
+      </c>
+      <c r="Q20" s="37">
+        <f t="shared" si="4"/>
+        <v>900000</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="6"/>
+        <v>5.9542425094393252</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="5"/>
+        <v>5.9542425094393252</v>
+      </c>
+      <c r="T20" t="s">
+        <v>61</v>
+      </c>
+      <c r="U20" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
+      <c r="A21" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B21" s="12">
+        <v>9.9542425094393252</v>
+      </c>
+      <c r="C21" s="12">
+        <v>5</v>
+      </c>
+      <c r="D21" s="12">
+        <v>9</v>
+      </c>
+      <c r="E21" s="40">
+        <v>1000000000</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>9.9542425094393252</v>
+      </c>
+      <c r="G21" s="38">
+        <f t="shared" si="1"/>
+        <v>9000000000</v>
+      </c>
+      <c r="I21" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="43" t="s">
+        <v>406</v>
+      </c>
+      <c r="K21" s="43">
+        <v>5</v>
+      </c>
+      <c r="L21" s="43">
+        <v>24</v>
+      </c>
+      <c r="M21" s="43">
+        <v>25</v>
+      </c>
+      <c r="N21" s="43">
+        <f t="shared" si="2"/>
+        <v>240000000</v>
+      </c>
+      <c r="O21" s="43">
+        <f t="shared" si="3"/>
+        <v>250000000</v>
+      </c>
+      <c r="P21" s="37">
+        <f t="shared" si="4"/>
+        <v>24000000</v>
+      </c>
+      <c r="Q21" s="37">
+        <f t="shared" si="4"/>
+        <v>25000000</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="6"/>
+        <v>7.3802112417116064</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="5"/>
+        <v>7.3979400086720375</v>
+      </c>
+      <c r="T21" t="s">
+        <v>61</v>
+      </c>
+      <c r="U21" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
+      <c r="A22" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B22" s="12">
+        <v>9.6989700043360187</v>
+      </c>
+      <c r="C22" s="12">
+        <v>5</v>
+      </c>
+      <c r="D22" s="12">
+        <v>5</v>
+      </c>
+      <c r="E22" s="40">
+        <v>1000000000</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>9.6989700043360187</v>
+      </c>
+      <c r="G22" s="38">
+        <f t="shared" si="1"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
+      <c r="A23" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B23" s="12">
+        <v>8.9030899869919438</v>
+      </c>
+      <c r="C23" s="12">
+        <v>4</v>
+      </c>
+      <c r="D23" s="12">
+        <v>8</v>
+      </c>
+      <c r="E23" s="40">
+        <v>100000000</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>8.9030899869919438</v>
+      </c>
+      <c r="G23" s="38">
+        <f t="shared" si="1"/>
+        <v>800000000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B24" s="12">
+        <v>9.2552725051033065</v>
+      </c>
+      <c r="C24" s="12">
+        <v>4</v>
+      </c>
+      <c r="D24" s="12">
+        <v>18</v>
+      </c>
+      <c r="E24" s="40">
+        <v>100000000</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>9.2552725051033065</v>
+      </c>
+      <c r="G24" s="38">
+        <f t="shared" si="1"/>
+        <v>1800000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25" s="12">
+        <v>8.9030899869919438</v>
+      </c>
+      <c r="C25" s="12">
+        <v>4</v>
+      </c>
+      <c r="D25" s="12">
+        <v>8</v>
+      </c>
+      <c r="E25" s="40">
+        <v>100000000</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>8.9030899869919438</v>
+      </c>
+      <c r="G25" s="38">
+        <f t="shared" si="1"/>
+        <v>800000000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" s="3"/>
+    </row>
+    <row r="27" spans="1:22">
+      <c r="A27" s="3"/>
+    </row>
+    <row r="28" spans="1:22">
+      <c r="A28" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
+      <c r="B29" s="43" t="s">
+        <v>386</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>422</v>
+      </c>
+      <c r="D29" t="s">
+        <v>423</v>
+      </c>
+      <c r="E29" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
+      <c r="B30" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" t="s">
+        <v>387</v>
+      </c>
+      <c r="E30">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
+      <c r="B31" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" t="s">
+        <v>387</v>
+      </c>
+      <c r="E31">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
+      <c r="B32" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" t="s">
+        <v>387</v>
+      </c>
+      <c r="E32">
+        <v>23000000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
+        <v>387</v>
+      </c>
+      <c r="E33">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" t="s">
+        <v>387</v>
+      </c>
+      <c r="E34">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" t="s">
+        <v>387</v>
+      </c>
+      <c r="E35">
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" t="s">
+        <v>387</v>
+      </c>
+      <c r="E36">
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" t="s">
+        <v>387</v>
+      </c>
+      <c r="E37">
+        <v>158113.8830084191</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" t="s">
+        <v>387</v>
+      </c>
+      <c r="E38">
+        <v>140000000</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="B39" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" t="s">
+        <v>387</v>
+      </c>
+      <c r="E39">
+        <v>260000000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="B40" s="43" t="s">
+        <v>403</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
+        <v>387</v>
+      </c>
+      <c r="E40">
+        <v>320000000</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="B41" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>387</v>
+      </c>
+      <c r="E41">
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="B42" s="43" t="s">
+        <v>404</v>
+      </c>
+      <c r="C42" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
+        <v>387</v>
+      </c>
+      <c r="E42">
+        <v>450000000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
+      <c r="B43" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>387</v>
+      </c>
+      <c r="E43">
+        <v>31000000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5">
+      <c r="B44" s="43" t="s">
+        <v>405</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>387</v>
+      </c>
+      <c r="E44">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5">
+      <c r="B45" s="43" t="s">
+        <v>406</v>
+      </c>
+      <c r="C45" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s">
+        <v>387</v>
+      </c>
+      <c r="E45">
+        <v>24000000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="C46" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" t="s">
+        <v>388</v>
+      </c>
+      <c r="E46">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5">
+      <c r="B47" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="C47" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" t="s">
+        <v>388</v>
+      </c>
+      <c r="E47">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5">
+      <c r="B48" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="C48" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" t="s">
+        <v>388</v>
+      </c>
+      <c r="E48">
+        <v>24000000</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="B49" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s">
+        <v>388</v>
+      </c>
+      <c r="E49">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="43" t="s">
+        <v>398</v>
+      </c>
+      <c r="C50" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" t="s">
+        <v>388</v>
+      </c>
+      <c r="E50">
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="B51" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="C51" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" t="s">
+        <v>388</v>
+      </c>
+      <c r="E51">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" t="s">
+        <v>388</v>
+      </c>
+      <c r="E52">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="B53" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="C53" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" t="s">
+        <v>388</v>
+      </c>
+      <c r="E53">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="B54" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="C54" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" t="s">
+        <v>388</v>
+      </c>
+      <c r="E54">
+        <v>3100000</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="B55" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="C55" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" t="s">
+        <v>388</v>
+      </c>
+      <c r="E55">
+        <v>284604.98941515438</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="C56" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" t="s">
+        <v>388</v>
+      </c>
+      <c r="E56">
+        <v>230000000</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" t="s">
+        <v>388</v>
+      </c>
+      <c r="E57">
+        <v>260000000</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58" s="43" t="s">
+        <v>403</v>
+      </c>
+      <c r="C58" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>388</v>
+      </c>
+      <c r="E58">
+        <v>470000000</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="B59" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>388</v>
+      </c>
+      <c r="E59">
+        <v>24000000</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5">
+      <c r="B60" s="43" t="s">
+        <v>404</v>
+      </c>
+      <c r="C60" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>388</v>
+      </c>
+      <c r="E60">
+        <v>720000000</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5">
+      <c r="B61" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" t="s">
+        <v>388</v>
+      </c>
+      <c r="E61">
+        <v>37000000</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5">
+      <c r="B62" s="43" t="s">
+        <v>405</v>
+      </c>
+      <c r="C62" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>388</v>
+      </c>
+      <c r="E62">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5">
+      <c r="B63" s="43" t="s">
+        <v>406</v>
+      </c>
+      <c r="C63" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>388</v>
+      </c>
+      <c r="E63">
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="B64" s="43" t="s">
+        <v>398</v>
+      </c>
+      <c r="C64" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" t="s">
+        <v>387</v>
+      </c>
+      <c r="E64" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="B65" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="C65" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" t="s">
+        <v>387</v>
+      </c>
+      <c r="E65" t="s">
+        <v>425</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="I2:N2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853016D0-ED39-534B-AEE3-E1C4990F581B}">
   <dimension ref="A1:AF28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32">
       <c r="A1" s="3" t="s">
         <v>25</v>
       </c>
@@ -2108,7 +4451,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32">
       <c r="A2" s="3" t="s">
         <v>56</v>
       </c>
@@ -2206,7 +4549,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32">
       <c r="A3" s="3" t="s">
         <v>73</v>
       </c>
@@ -2304,7 +4647,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32">
       <c r="A4" s="3" t="s">
         <v>86</v>
       </c>
@@ -2402,7 +4745,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32">
       <c r="A5" s="3" t="s">
         <v>99</v>
       </c>
@@ -2500,7 +4843,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32">
       <c r="A6" s="3" t="s">
         <v>113</v>
       </c>
@@ -2598,7 +4941,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32">
       <c r="A7" s="3" t="s">
         <v>123</v>
       </c>
@@ -2696,7 +5039,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32">
       <c r="A8" s="3" t="s">
         <v>136</v>
       </c>
@@ -2794,7 +5137,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32">
       <c r="A9" s="3" t="s">
         <v>149</v>
       </c>
@@ -2892,7 +5235,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32">
       <c r="A10" s="3" t="s">
         <v>159</v>
       </c>
@@ -2990,7 +5333,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32">
       <c r="A11" s="3" t="s">
         <v>172</v>
       </c>
@@ -3088,7 +5431,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32">
       <c r="A12" s="3" t="s">
         <v>184</v>
       </c>
@@ -3186,7 +5529,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32">
       <c r="A13" s="3" t="s">
         <v>194</v>
       </c>
@@ -3284,7 +5627,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32">
       <c r="A14" s="3" t="s">
         <v>206</v>
       </c>
@@ -3382,7 +5725,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32">
       <c r="A15" s="3" t="s">
         <v>213</v>
       </c>
@@ -3480,7 +5823,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32">
       <c r="A16" s="3" t="s">
         <v>226</v>
       </c>
@@ -3578,7 +5921,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32">
       <c r="A17" s="3" t="s">
         <v>238</v>
       </c>
@@ -3676,7 +6019,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32">
       <c r="A18" s="3" t="s">
         <v>251</v>
       </c>
@@ -3774,7 +6117,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32">
       <c r="A19" s="3" t="s">
         <v>263</v>
       </c>
@@ -3872,7 +6215,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32">
       <c r="A20" s="3" t="s">
         <v>272</v>
       </c>
@@ -3970,7 +6313,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32">
       <c r="A21" s="3" t="s">
         <v>282</v>
       </c>
@@ -4068,7 +6411,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32">
       <c r="A22" s="3" t="s">
         <v>291</v>
       </c>
@@ -4166,7 +6509,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32">
       <c r="A23" s="3" t="s">
         <v>299</v>
       </c>
@@ -4264,7 +6607,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32">
       <c r="A24" s="3" t="s">
         <v>311</v>
       </c>
@@ -4362,7 +6705,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32">
       <c r="A25" s="3" t="s">
         <v>319</v>
       </c>
@@ -4460,7 +6803,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32">
       <c r="A26" t="s">
         <v>328</v>
       </c>
@@ -4504,7 +6847,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32">
       <c r="A27" t="s">
         <v>328</v>
       </c>
@@ -4548,7 +6891,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32">
       <c r="A28" t="s">
         <v>328</v>
       </c>
@@ -4597,10 +6940,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D4B194-C8BE-864D-B727-FDE86CBA906A}">
-  <dimension ref="B1:Q63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:S89"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="10.33203125" customWidth="1"/>
     <col min="3" max="3" width="8.6640625" customWidth="1"/>
@@ -4608,34 +6951,35 @@
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="9" width="13.5" customWidth="1"/>
     <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="15" max="15" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:17">
       <c r="C1" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="2" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="39" t="s">
+    <row r="2" spans="2:17" ht="17" thickBot="1">
+      <c r="D2" s="69" t="s">
         <v>338</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
       <c r="M2" s="15"/>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="70" t="s">
         <v>339</v>
       </c>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-    </row>
-    <row r="3" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+    </row>
+    <row r="3" spans="2:17" ht="17" thickBot="1">
       <c r="D3" s="16">
         <v>46091</v>
       </c>
@@ -4665,7 +7009,7 @@
       </c>
       <c r="M3" s="18"/>
     </row>
-    <row r="4" spans="2:17" s="25" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" s="25" customFormat="1" ht="17" thickBot="1">
       <c r="B4" t="s">
         <v>340</v>
       </c>
@@ -4715,7 +7059,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:17">
       <c r="C5" s="12" t="s">
         <v>356</v>
       </c>
@@ -4762,7 +7106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:17">
       <c r="C6" s="12" t="s">
         <v>77</v>
       </c>
@@ -4809,7 +7153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:17">
       <c r="C7" s="12" t="s">
         <v>255</v>
       </c>
@@ -4856,7 +7200,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:17">
       <c r="C8" s="28" t="s">
         <v>276</v>
       </c>
@@ -4903,7 +7247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:17">
       <c r="C9" s="12" t="s">
         <v>267</v>
       </c>
@@ -4950,7 +7294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:17">
       <c r="C10" s="28" t="s">
         <v>188</v>
       </c>
@@ -4997,7 +7341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:17">
       <c r="C11" s="12" t="s">
         <v>163</v>
       </c>
@@ -5044,7 +7388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" ht="17" thickBot="1">
       <c r="C12" s="12" t="s">
         <v>295</v>
       </c>
@@ -5091,7 +7435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:17">
       <c r="O14" t="s">
         <v>357</v>
       </c>
@@ -5102,7 +7446,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="17" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" ht="17" thickBot="1">
       <c r="C17" t="s">
         <v>340</v>
       </c>
@@ -5110,7 +7454,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" ht="17" thickBot="1">
       <c r="C18" s="19" t="s">
         <v>341</v>
       </c>
@@ -5145,7 +7489,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="19" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" ht="17" thickBot="1">
       <c r="B19" s="16">
         <v>46091</v>
       </c>
@@ -5187,7 +7531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" ht="17" thickBot="1">
       <c r="B20" s="16">
         <v>46092</v>
       </c>
@@ -5229,7 +7573,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" ht="17" thickBot="1">
       <c r="B21" s="16">
         <v>46093</v>
       </c>
@@ -5271,7 +7615,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" ht="17" thickBot="1">
       <c r="B22" s="16">
         <v>46094</v>
       </c>
@@ -5313,7 +7657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" ht="17" thickBot="1">
       <c r="B23" s="16">
         <v>46095</v>
       </c>
@@ -5355,7 +7699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" ht="17" thickBot="1">
       <c r="B24" s="16">
         <v>46096</v>
       </c>
@@ -5397,7 +7741,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" ht="17" thickBot="1">
       <c r="B25" s="16">
         <v>46097</v>
       </c>
@@ -5439,7 +7783,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" ht="17" thickBot="1">
       <c r="B26" s="16">
         <v>46098</v>
       </c>
@@ -5481,7 +7825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" ht="17" thickBot="1">
       <c r="B27" s="17">
         <v>46099</v>
       </c>
@@ -5523,7 +7867,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:15">
       <c r="B28" s="18"/>
       <c r="D28" s="12" t="s">
         <v>351</v>
@@ -5541,7 +7885,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:15">
       <c r="E30">
         <f>SUM(E19:E27)/E28</f>
         <v>1</v>
@@ -5559,7 +7903,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16" ht="17" thickBot="1">
       <c r="C35" t="s">
         <v>340</v>
       </c>
@@ -5567,7 +7911,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="36" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:16" ht="17" thickBot="1">
       <c r="C36" s="19" t="s">
         <v>341</v>
       </c>
@@ -5608,7 +7952,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="37" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" ht="17" thickBot="1">
       <c r="B37" s="16">
         <v>46091</v>
       </c>
@@ -5657,7 +8001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16" ht="17" thickBot="1">
       <c r="B38" s="16">
         <v>46092</v>
       </c>
@@ -5706,7 +8050,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16" ht="17" thickBot="1">
       <c r="B39" s="16">
         <v>46093</v>
       </c>
@@ -5755,7 +8099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" ht="17" thickBot="1">
       <c r="B40" s="16">
         <v>46094</v>
       </c>
@@ -5804,7 +8148,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:16" ht="17" thickBot="1">
       <c r="B41" s="16">
         <v>46095</v>
       </c>
@@ -5853,7 +8197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:16" ht="17" thickBot="1">
       <c r="B42" s="16">
         <v>46096</v>
       </c>
@@ -5902,7 +8246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" ht="17" thickBot="1">
       <c r="B43" s="16">
         <v>46097</v>
       </c>
@@ -5951,7 +8295,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:16" ht="17" thickBot="1">
       <c r="B44" s="16">
         <v>46098</v>
       </c>
@@ -6000,7 +8344,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:16" ht="17" thickBot="1">
       <c r="B45" s="17">
         <v>46099</v>
       </c>
@@ -6049,7 +8393,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16">
       <c r="B46" s="18"/>
       <c r="D46" s="12" t="s">
         <v>351</v>
@@ -6075,7 +8419,7 @@
       <c r="M46" s="36"/>
       <c r="N46" s="36"/>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16">
       <c r="E48">
         <f>SUM(E37:E45)/E46</f>
         <v>1</v>
@@ -6097,8 +8441,8 @@
         <v>0.2857142857142857</v>
       </c>
     </row>
-    <row r="50" spans="4:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="4:8" ht="17" thickBot="1"/>
+    <row r="51" spans="4:8">
       <c r="E51" s="22" t="s">
         <v>352</v>
       </c>
@@ -6112,7 +8456,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="4:8">
       <c r="D52" s="12" t="s">
         <v>356</v>
       </c>
@@ -6129,7 +8473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="4:8">
       <c r="D53" s="28" t="s">
         <v>188</v>
       </c>
@@ -6146,7 +8490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="4:8">
       <c r="D54" s="28" t="s">
         <v>276</v>
       </c>
@@ -6163,7 +8507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="4:8">
       <c r="D55" s="12" t="s">
         <v>77</v>
       </c>
@@ -6180,8 +8524,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="4:8" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="4:8" ht="17" thickBot="1"/>
+    <row r="58" spans="4:8">
       <c r="D58" s="12" t="s">
         <v>351</v>
       </c>
@@ -6198,7 +8542,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="4:8">
       <c r="D59" s="12" t="s">
         <v>356</v>
       </c>
@@ -6215,7 +8559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="4:8">
       <c r="D60" s="12" t="s">
         <v>267</v>
       </c>
@@ -6232,7 +8576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="4:8">
       <c r="D61" s="12" t="s">
         <v>163</v>
       </c>
@@ -6249,7 +8593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="4:8">
       <c r="D62" s="12" t="s">
         <v>255</v>
       </c>
@@ -6266,7 +8610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="4:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:8" ht="17" thickBot="1">
       <c r="D63" s="12" t="s">
         <v>295</v>
       </c>
@@ -6282,6 +8626,627 @@
       <c r="H63" s="30">
         <v>0</v>
       </c>
+    </row>
+    <row r="66" spans="1:19">
+      <c r="A66" s="54" t="s">
+        <v>413</v>
+      </c>
+      <c r="B66" s="54"/>
+      <c r="C66" s="54"/>
+      <c r="D66" s="54"/>
+      <c r="E66" s="54"/>
+      <c r="F66" s="54"/>
+    </row>
+    <row r="67" spans="1:19">
+      <c r="A67" s="54"/>
+      <c r="B67" s="54"/>
+      <c r="C67" s="54" t="s">
+        <v>373</v>
+      </c>
+      <c r="D67" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="E67" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="F67" s="54"/>
+    </row>
+    <row r="68" spans="1:19">
+      <c r="A68" s="54"/>
+      <c r="B68" s="55" t="s">
+        <v>356</v>
+      </c>
+      <c r="C68" s="54">
+        <f>E68-D68</f>
+        <v>5</v>
+      </c>
+      <c r="D68" s="54">
+        <v>18</v>
+      </c>
+      <c r="E68" s="56">
+        <v>23</v>
+      </c>
+      <c r="F68" s="54"/>
+    </row>
+    <row r="69" spans="1:19">
+      <c r="A69" s="54"/>
+      <c r="B69" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="C69" s="54">
+        <f t="shared" ref="C69:C75" si="2">E69-D69</f>
+        <v>18</v>
+      </c>
+      <c r="D69" s="54">
+        <v>4</v>
+      </c>
+      <c r="E69" s="55">
+        <v>22</v>
+      </c>
+      <c r="F69" s="54"/>
+    </row>
+    <row r="70" spans="1:19">
+      <c r="A70" s="54"/>
+      <c r="B70" s="55" t="s">
+        <v>255</v>
+      </c>
+      <c r="C70" s="54">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="D70" s="54">
+        <v>9</v>
+      </c>
+      <c r="E70" s="55">
+        <v>23</v>
+      </c>
+      <c r="F70" s="54"/>
+    </row>
+    <row r="71" spans="1:19">
+      <c r="A71" s="54"/>
+      <c r="B71" s="57" t="s">
+        <v>276</v>
+      </c>
+      <c r="C71" s="54">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="D71" s="54">
+        <v>14</v>
+      </c>
+      <c r="E71" s="55">
+        <v>24</v>
+      </c>
+      <c r="F71" s="54"/>
+    </row>
+    <row r="72" spans="1:19">
+      <c r="A72" s="54"/>
+      <c r="B72" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="C72" s="54">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="D72" s="54">
+        <v>20</v>
+      </c>
+      <c r="E72" s="55">
+        <v>24</v>
+      </c>
+      <c r="F72" s="54"/>
+    </row>
+    <row r="73" spans="1:19">
+      <c r="A73" s="54"/>
+      <c r="B73" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="C73" s="54">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="D73" s="54">
+        <v>18</v>
+      </c>
+      <c r="E73" s="55">
+        <v>22</v>
+      </c>
+      <c r="F73" s="54"/>
+    </row>
+    <row r="74" spans="1:19">
+      <c r="A74" s="54"/>
+      <c r="B74" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="C74" s="54">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="D74" s="54">
+        <v>17</v>
+      </c>
+      <c r="E74" s="55">
+        <v>19</v>
+      </c>
+      <c r="F74" s="54"/>
+    </row>
+    <row r="75" spans="1:19" ht="17" thickBot="1">
+      <c r="A75" s="54"/>
+      <c r="B75" s="55" t="s">
+        <v>295</v>
+      </c>
+      <c r="C75" s="54">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="D75" s="58">
+        <v>0</v>
+      </c>
+      <c r="E75" s="55">
+        <v>21</v>
+      </c>
+      <c r="F75" s="54"/>
+    </row>
+    <row r="76" spans="1:19">
+      <c r="A76" s="54"/>
+      <c r="B76" s="54"/>
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="54"/>
+      <c r="F76" s="54"/>
+    </row>
+    <row r="77" spans="1:19">
+      <c r="A77" s="54"/>
+      <c r="B77" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" s="54" t="s">
+        <v>373</v>
+      </c>
+      <c r="D77" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="E77" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="F77" s="54"/>
+      <c r="I77" s="61" t="s">
+        <v>417</v>
+      </c>
+      <c r="J77" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="K77" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="L77" s="61" t="s">
+        <v>420</v>
+      </c>
+      <c r="M77" s="61"/>
+      <c r="O77" s="61" t="s">
+        <v>417</v>
+      </c>
+      <c r="P77" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q77" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="R77" s="61" t="s">
+        <v>420</v>
+      </c>
+      <c r="S77" s="61"/>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" s="54"/>
+      <c r="B78" s="55" t="s">
+        <v>356</v>
+      </c>
+      <c r="C78" s="54">
+        <f>E78-D78</f>
+        <v>5</v>
+      </c>
+      <c r="D78" s="54">
+        <v>18</v>
+      </c>
+      <c r="E78" s="56">
+        <v>23</v>
+      </c>
+      <c r="F78" s="54"/>
+      <c r="G78" s="54" t="s">
+        <v>413</v>
+      </c>
+      <c r="I78" s="62" t="s">
+        <v>356</v>
+      </c>
+      <c r="J78" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="K78" s="63">
+        <v>2.556336E-4</v>
+      </c>
+      <c r="L78" s="62">
+        <v>3.834504E-4</v>
+      </c>
+      <c r="M78" s="62"/>
+      <c r="O78" s="62" t="s">
+        <v>356</v>
+      </c>
+      <c r="P78" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q78" s="62">
+        <v>2.7454184999999999E-2</v>
+      </c>
+      <c r="R78" s="62">
+        <v>9.1513949999999997E-2</v>
+      </c>
+      <c r="S78" s="62"/>
+    </row>
+    <row r="79" spans="1:19">
+      <c r="A79" s="54"/>
+      <c r="B79" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="C79" s="54">
+        <f t="shared" ref="C79:C81" si="3">E79-D79</f>
+        <v>18</v>
+      </c>
+      <c r="D79" s="54">
+        <v>4</v>
+      </c>
+      <c r="E79" s="55">
+        <v>22</v>
+      </c>
+      <c r="F79" s="54"/>
+      <c r="G79" s="60" t="s">
+        <v>415</v>
+      </c>
+      <c r="I79" s="62" t="s">
+        <v>356</v>
+      </c>
+      <c r="J79" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="K79" s="63">
+        <v>1</v>
+      </c>
+      <c r="L79" s="62">
+        <v>1</v>
+      </c>
+      <c r="M79" s="62"/>
+      <c r="O79" s="62" t="s">
+        <v>356</v>
+      </c>
+      <c r="P79" s="62" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q79" s="62">
+        <v>0.95489009700000005</v>
+      </c>
+      <c r="R79" s="62">
+        <v>0.95489009999999996</v>
+      </c>
+      <c r="S79" s="62"/>
+    </row>
+    <row r="80" spans="1:19">
+      <c r="A80" s="54"/>
+      <c r="B80" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="C80" s="54">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="D80" s="54">
+        <v>18</v>
+      </c>
+      <c r="E80" s="55">
+        <v>22</v>
+      </c>
+      <c r="F80" s="54"/>
+      <c r="G80" t="s">
+        <v>414</v>
+      </c>
+      <c r="I80" s="62" t="s">
+        <v>356</v>
+      </c>
+      <c r="J80" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="K80" s="63">
+        <v>1.153547E-7</v>
+      </c>
+      <c r="L80" s="62">
+        <v>3.4606420000000001E-7</v>
+      </c>
+      <c r="M80" s="62"/>
+      <c r="O80" s="62" t="s">
+        <v>356</v>
+      </c>
+      <c r="P80" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q80" s="62">
+        <v>0.68163394899999996</v>
+      </c>
+      <c r="R80" s="62">
+        <v>0.85204243999999996</v>
+      </c>
+      <c r="S80" s="62"/>
+    </row>
+    <row r="81" spans="1:19" ht="17" thickBot="1">
+      <c r="A81" s="54"/>
+      <c r="B81" s="55" t="s">
+        <v>295</v>
+      </c>
+      <c r="C81" s="54">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="D81" s="58">
+        <v>0</v>
+      </c>
+      <c r="E81" s="55">
+        <v>21</v>
+      </c>
+      <c r="F81" s="54"/>
+      <c r="I81" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="J81" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="K81" s="63">
+        <v>8.3559370000000003E-5</v>
+      </c>
+      <c r="L81" s="62">
+        <v>1.671187E-4</v>
+      </c>
+      <c r="M81" s="62"/>
+      <c r="O81" s="62" t="s">
+        <v>356</v>
+      </c>
+      <c r="P81" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q81" s="62">
+        <v>0.37927554899999999</v>
+      </c>
+      <c r="R81" s="62">
+        <v>0.62751926000000002</v>
+      </c>
+      <c r="S81" s="62"/>
+    </row>
+    <row r="82" spans="1:19">
+      <c r="A82" s="54"/>
+      <c r="B82" s="54"/>
+      <c r="C82" s="54"/>
+      <c r="D82" s="54"/>
+      <c r="E82" s="54"/>
+      <c r="F82" s="54"/>
+      <c r="I82" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="J82" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="K82" s="63">
+        <v>0.15089350000000001</v>
+      </c>
+      <c r="L82" s="62">
+        <v>0.18107210000000001</v>
+      </c>
+      <c r="M82" s="62"/>
+      <c r="O82" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="P82" s="62" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q82" s="62">
+        <v>7.4026420000000001E-3</v>
+      </c>
+      <c r="R82" s="62">
+        <v>3.7013209999999998E-2</v>
+      </c>
+      <c r="S82" s="62"/>
+    </row>
+    <row r="83" spans="1:19">
+      <c r="A83" s="54"/>
+      <c r="B83" s="54"/>
+      <c r="C83" s="54"/>
+      <c r="D83" s="54"/>
+      <c r="E83" s="54"/>
+      <c r="F83" s="54"/>
+      <c r="I83" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="J83" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="K83" s="63">
+        <v>2.6022120000000002E-8</v>
+      </c>
+      <c r="L83" s="62">
+        <v>1.5613270000000001E-7</v>
+      </c>
+      <c r="M83" s="62"/>
+      <c r="O83" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="P83" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q83" s="62">
+        <v>3.0403169999999998E-3</v>
+      </c>
+      <c r="R83" s="62">
+        <v>3.040317E-2</v>
+      </c>
+      <c r="S83" s="62"/>
+    </row>
+    <row r="84" spans="1:19">
+      <c r="A84" s="54"/>
+      <c r="B84" s="54" t="s">
+        <v>166</v>
+      </c>
+      <c r="C84" s="54" t="s">
+        <v>373</v>
+      </c>
+      <c r="D84" s="54" t="s">
+        <v>410</v>
+      </c>
+      <c r="E84" s="54" t="s">
+        <v>411</v>
+      </c>
+      <c r="F84" s="54"/>
+      <c r="G84" s="54" t="s">
+        <v>413</v>
+      </c>
+      <c r="O84" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="P84" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q84" s="62">
+        <v>0.43926347999999998</v>
+      </c>
+      <c r="R84" s="62">
+        <v>0.62751926000000002</v>
+      </c>
+      <c r="S84" s="62"/>
+    </row>
+    <row r="85" spans="1:19">
+      <c r="A85" s="54"/>
+      <c r="B85" s="55" t="s">
+        <v>356</v>
+      </c>
+      <c r="C85" s="54">
+        <f>E85-D85</f>
+        <v>5</v>
+      </c>
+      <c r="D85" s="54">
+        <v>18</v>
+      </c>
+      <c r="E85" s="56">
+        <v>23</v>
+      </c>
+      <c r="F85" s="54"/>
+      <c r="G85" s="60" t="s">
+        <v>416</v>
+      </c>
+      <c r="O85" s="62" t="s">
+        <v>267</v>
+      </c>
+      <c r="P85" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q85" s="62">
+        <v>0.89289347399999996</v>
+      </c>
+      <c r="R85" s="62">
+        <v>0.95489009999999996</v>
+      </c>
+      <c r="S85" s="62"/>
+    </row>
+    <row r="86" spans="1:19">
+      <c r="A86" s="54"/>
+      <c r="B86" s="55" t="s">
+        <v>255</v>
+      </c>
+      <c r="C86" s="54">
+        <f t="shared" ref="C86:C88" si="4">E86-D86</f>
+        <v>14</v>
+      </c>
+      <c r="D86" s="54">
+        <v>9</v>
+      </c>
+      <c r="E86" s="55">
+        <v>23</v>
+      </c>
+      <c r="F86" s="54"/>
+      <c r="G86" t="s">
+        <v>414</v>
+      </c>
+      <c r="O86" s="62" t="s">
+        <v>267</v>
+      </c>
+      <c r="P86" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q86" s="62">
+        <v>0.15929502300000001</v>
+      </c>
+      <c r="R86" s="62">
+        <v>0.31859005000000001</v>
+      </c>
+      <c r="S86" s="62"/>
+    </row>
+    <row r="87" spans="1:19">
+      <c r="A87" s="54"/>
+      <c r="B87" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="C87" s="54">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="D87" s="54">
+        <v>20</v>
+      </c>
+      <c r="E87" s="55">
+        <v>24</v>
+      </c>
+      <c r="F87" s="54"/>
+      <c r="O87" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="P87" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q87" s="62">
+        <v>7.9737840000000004E-2</v>
+      </c>
+      <c r="R87" s="62">
+        <v>0.19934460000000001</v>
+      </c>
+      <c r="S87" s="62"/>
+    </row>
+    <row r="88" spans="1:19">
+      <c r="A88" s="54"/>
+      <c r="B88" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="C88" s="54">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="D88" s="54">
+        <v>17</v>
+      </c>
+      <c r="E88" s="55">
+        <v>19</v>
+      </c>
+      <c r="F88" s="54"/>
+    </row>
+    <row r="89" spans="1:19">
+      <c r="A89" s="54"/>
+      <c r="B89" s="59" t="s">
+        <v>276</v>
+      </c>
+      <c r="C89" s="54">
+        <f>E89-D89</f>
+        <v>10</v>
+      </c>
+      <c r="D89" s="54">
+        <v>14</v>
+      </c>
+      <c r="E89" s="55">
+        <v>24</v>
+      </c>
+      <c r="F89" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6290,4 +9255,936 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE0842A1-26BA-6A4F-A252-2631199E30EB}">
+  <dimension ref="A1:P33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>371</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="37">
+        <v>1</v>
+      </c>
+      <c r="D2" s="39">
+        <v>1E-4</v>
+      </c>
+      <c r="E2" s="37">
+        <v>10</v>
+      </c>
+      <c r="F2" s="39">
+        <v>10000000</v>
+      </c>
+      <c r="G2" s="39">
+        <v>1000000</v>
+      </c>
+      <c r="H2" s="37"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="C3" s="37">
+        <v>2</v>
+      </c>
+      <c r="D3" s="39">
+        <v>1E-4</v>
+      </c>
+      <c r="E3" s="37">
+        <v>38</v>
+      </c>
+      <c r="F3" s="39">
+        <v>38000000</v>
+      </c>
+      <c r="G3" s="39">
+        <v>3800000</v>
+      </c>
+      <c r="H3" s="37"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="C4" s="37">
+        <v>3</v>
+      </c>
+      <c r="D4" s="39">
+        <v>1E-4</v>
+      </c>
+      <c r="E4" s="37">
+        <v>19</v>
+      </c>
+      <c r="F4" s="39">
+        <v>19000000</v>
+      </c>
+      <c r="G4" s="39">
+        <v>1900000</v>
+      </c>
+      <c r="H4" s="37"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" s="37">
+        <v>4</v>
+      </c>
+      <c r="D5" s="39">
+        <v>1E-3</v>
+      </c>
+      <c r="E5" s="37">
+        <v>26</v>
+      </c>
+      <c r="F5" s="39">
+        <v>2600000</v>
+      </c>
+      <c r="G5" s="39">
+        <v>260000</v>
+      </c>
+      <c r="H5" s="37"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="37">
+        <v>1</v>
+      </c>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37">
+        <v>0</v>
+      </c>
+      <c r="H6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="37"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="37">
+        <v>2</v>
+      </c>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37">
+        <v>0</v>
+      </c>
+      <c r="H7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="37"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="37">
+        <v>3</v>
+      </c>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37">
+        <v>0</v>
+      </c>
+      <c r="H8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="37"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="37">
+        <v>4</v>
+      </c>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37">
+        <v>0</v>
+      </c>
+      <c r="H9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="37"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="44">
+        <v>1</v>
+      </c>
+      <c r="D10" s="45">
+        <v>1E-4</v>
+      </c>
+      <c r="E10" s="44">
+        <v>23</v>
+      </c>
+      <c r="F10" s="45">
+        <v>23000000</v>
+      </c>
+      <c r="G10" s="45">
+        <v>2300000</v>
+      </c>
+      <c r="H10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="37"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="44">
+        <v>2</v>
+      </c>
+      <c r="D11" s="45">
+        <v>1E-4</v>
+      </c>
+      <c r="E11" s="44">
+        <v>22</v>
+      </c>
+      <c r="F11" s="45">
+        <v>22000000</v>
+      </c>
+      <c r="G11" s="45">
+        <v>2200000</v>
+      </c>
+      <c r="H11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="37"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="C12" s="44">
+        <v>3</v>
+      </c>
+      <c r="D12" s="45">
+        <v>1E-4</v>
+      </c>
+      <c r="E12" s="44">
+        <v>23</v>
+      </c>
+      <c r="F12" s="45">
+        <v>23000000</v>
+      </c>
+      <c r="G12" s="45">
+        <v>2300000</v>
+      </c>
+      <c r="H12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="37"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="C13" s="44">
+        <v>4</v>
+      </c>
+      <c r="D13" s="45">
+        <v>1E-4</v>
+      </c>
+      <c r="E13" s="44">
+        <v>10</v>
+      </c>
+      <c r="F13" s="45">
+        <v>10000000</v>
+      </c>
+      <c r="G13" s="45">
+        <v>1000000</v>
+      </c>
+      <c r="H13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="37"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="46">
+        <v>1</v>
+      </c>
+      <c r="D14" s="47">
+        <v>1E-3</v>
+      </c>
+      <c r="E14" s="46">
+        <v>3</v>
+      </c>
+      <c r="F14" s="47">
+        <v>300000</v>
+      </c>
+      <c r="G14" s="47">
+        <v>30000</v>
+      </c>
+      <c r="H14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="37"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" s="46">
+        <v>2</v>
+      </c>
+      <c r="D15" s="47">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="E15" s="46">
+        <v>11</v>
+      </c>
+      <c r="F15" s="47">
+        <v>110000000</v>
+      </c>
+      <c r="G15" s="47">
+        <v>11000000</v>
+      </c>
+      <c r="H15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="37"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="37"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="C16" s="46">
+        <v>3</v>
+      </c>
+      <c r="D16" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="E16" s="46">
+        <v>19</v>
+      </c>
+      <c r="F16" s="47">
+        <v>190000</v>
+      </c>
+      <c r="G16" s="47">
+        <v>19000</v>
+      </c>
+      <c r="H16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="37"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="37"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>255</v>
+      </c>
+      <c r="C17" s="46">
+        <v>4</v>
+      </c>
+      <c r="D17" s="47">
+        <v>0.01</v>
+      </c>
+      <c r="E17" s="46">
+        <v>4</v>
+      </c>
+      <c r="F17" s="47">
+        <v>40000</v>
+      </c>
+      <c r="G17" s="47">
+        <v>4000</v>
+      </c>
+      <c r="H17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="37"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="36">
+        <v>1</v>
+      </c>
+      <c r="D18" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E18" s="36">
+        <v>7</v>
+      </c>
+      <c r="F18" s="51">
+        <v>70000</v>
+      </c>
+      <c r="G18" s="51">
+        <v>7000</v>
+      </c>
+      <c r="H18" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="37"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="C19" s="36">
+        <v>2</v>
+      </c>
+      <c r="D19" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E19" s="36">
+        <v>3</v>
+      </c>
+      <c r="F19" s="51">
+        <v>30000</v>
+      </c>
+      <c r="G19" s="51">
+        <v>3000</v>
+      </c>
+      <c r="H19" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="37"/>
+      <c r="P19" s="37"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" s="36">
+        <v>3</v>
+      </c>
+      <c r="D20" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E20" s="36">
+        <v>6</v>
+      </c>
+      <c r="F20" s="51">
+        <v>60000</v>
+      </c>
+      <c r="G20" s="51">
+        <v>6000</v>
+      </c>
+      <c r="H20" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="37"/>
+      <c r="P20" s="37"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21" s="36">
+        <v>4</v>
+      </c>
+      <c r="D21" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="E21" s="36">
+        <v>2</v>
+      </c>
+      <c r="F21" s="51">
+        <v>20000</v>
+      </c>
+      <c r="G21" s="51">
+        <v>2000</v>
+      </c>
+      <c r="H21" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="37"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="37">
+        <v>1</v>
+      </c>
+      <c r="D22" s="39">
+        <v>0.01</v>
+      </c>
+      <c r="E22" s="37">
+        <v>25</v>
+      </c>
+      <c r="F22" s="39">
+        <v>250000</v>
+      </c>
+      <c r="G22" s="39">
+        <v>25000</v>
+      </c>
+      <c r="H22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
+      <c r="P22" s="37"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="37">
+        <v>2</v>
+      </c>
+      <c r="D23" s="39">
+        <v>1E-4</v>
+      </c>
+      <c r="E23" s="37">
+        <v>6</v>
+      </c>
+      <c r="F23" s="39">
+        <v>6000000</v>
+      </c>
+      <c r="G23" s="39">
+        <v>600000</v>
+      </c>
+      <c r="H23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+      <c r="P23" s="37"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="37">
+        <v>3</v>
+      </c>
+      <c r="D24" s="39">
+        <v>1E-3</v>
+      </c>
+      <c r="E24" s="37">
+        <v>61</v>
+      </c>
+      <c r="F24" s="39">
+        <v>6100000</v>
+      </c>
+      <c r="G24" s="39">
+        <v>610000</v>
+      </c>
+      <c r="H24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="37"/>
+      <c r="P24" s="37"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="37">
+        <v>4</v>
+      </c>
+      <c r="D25" s="39">
+        <v>1E-3</v>
+      </c>
+      <c r="E25" s="37">
+        <v>15</v>
+      </c>
+      <c r="F25" s="39">
+        <v>1500000</v>
+      </c>
+      <c r="G25" s="39">
+        <v>150000</v>
+      </c>
+      <c r="H25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" s="49">
+        <v>1</v>
+      </c>
+      <c r="D26" s="50">
+        <v>0.01</v>
+      </c>
+      <c r="E26" s="49">
+        <v>45</v>
+      </c>
+      <c r="F26" s="50">
+        <v>450000</v>
+      </c>
+      <c r="G26" s="50">
+        <v>45000</v>
+      </c>
+      <c r="H26" s="37"/>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C27" s="49">
+        <v>2</v>
+      </c>
+      <c r="D27" s="50">
+        <v>1E-3</v>
+      </c>
+      <c r="E27" s="49">
+        <v>24</v>
+      </c>
+      <c r="F27" s="50">
+        <v>2400000</v>
+      </c>
+      <c r="G27" s="50">
+        <v>240000</v>
+      </c>
+      <c r="H27" s="37"/>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="49">
+        <v>3</v>
+      </c>
+      <c r="D28" s="50">
+        <v>0.01</v>
+      </c>
+      <c r="E28" s="49">
+        <v>147</v>
+      </c>
+      <c r="F28" s="50">
+        <v>1470000</v>
+      </c>
+      <c r="G28" s="50">
+        <v>147000</v>
+      </c>
+      <c r="H28" s="37"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C29" s="49">
+        <v>4</v>
+      </c>
+      <c r="D29" s="50">
+        <v>0.01</v>
+      </c>
+      <c r="E29" s="49">
+        <v>33</v>
+      </c>
+      <c r="F29" s="50">
+        <v>330000</v>
+      </c>
+      <c r="G29" s="50">
+        <v>33000</v>
+      </c>
+      <c r="H29" s="37"/>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52">
+        <v>0</v>
+      </c>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="37"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="37"/>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52">
+        <v>0</v>
+      </c>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="37"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="37"/>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52">
+        <v>0</v>
+      </c>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="37"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="37"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52">
+        <v>0</v>
+      </c>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="37"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>